--- a/results/part2_step2_forecasting/forecast_results.xlsx
+++ b/results/part2_step2_forecasting/forecast_results.xlsx
@@ -10,11 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model_Comparison" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By_Horizon" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Train_Test_Split" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final_Forecast_Total" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final_Forecast" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final_Forecast_Total" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interval_Coverage" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2513,177 +2510,399 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>week_id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>learns_from_weeks</t>
+          <t>demand_forecast</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>years_of_history</t>
+          <t>demand_p10</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>forecasts_weeks</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>forecasts_made</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>compared_with_reality</t>
+          <t>demand_p90</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1-156</t>
-        </is>
+      <c r="A2" t="n">
+        <v>261</v>
+      </c>
+      <c r="B2" t="n">
+        <v>67688.7</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>157-182</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>780</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
+        <v>62317.2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>73059.7</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Test 2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1-182</t>
-        </is>
+      <c r="A3" t="n">
+        <v>262</v>
+      </c>
+      <c r="B3" t="n">
+        <v>69682.89999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>183-208</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>780</v>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
+        <v>64153.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>75212.10000000001</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Test 3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1-208</t>
-        </is>
+      <c r="A4" t="n">
+        <v>263</v>
+      </c>
+      <c r="B4" t="n">
+        <v>71623.60000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>209-234</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>780</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
+        <v>65939.8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>77306.8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Test 4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1-234</t>
-        </is>
+      <c r="A5" t="n">
+        <v>264</v>
+      </c>
+      <c r="B5" t="n">
+        <v>73488.39999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>235-260</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>780</v>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
+        <v>67656.7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>79319.60000000001</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Final forecast</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1-260</t>
-        </is>
+      <c r="A6" t="n">
+        <v>265</v>
+      </c>
+      <c r="B6" t="n">
+        <v>75256</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>261-286</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>780</v>
-      </c>
-      <c r="F6" t="b">
-        <v>0</v>
+        <v>69508.7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>80801.89999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>266</v>
+      </c>
+      <c r="B7" t="n">
+        <v>76904.89999999999</v>
+      </c>
+      <c r="C7" t="n">
+        <v>71031.7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>82572.39999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>267</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78413.39999999999</v>
+      </c>
+      <c r="C8" t="n">
+        <v>72425</v>
+      </c>
+      <c r="D8" t="n">
+        <v>84192</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>268</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79758.89999999999</v>
+      </c>
+      <c r="C9" t="n">
+        <v>73667.8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>85636.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>269</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80918.2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>74738.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>86881.39999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>270</v>
+      </c>
+      <c r="B11" t="n">
+        <v>81868</v>
+      </c>
+      <c r="C11" t="n">
+        <v>75615.8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>87901.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>271</v>
+      </c>
+      <c r="B12" t="n">
+        <v>82586.39999999999</v>
+      </c>
+      <c r="C12" t="n">
+        <v>76279.3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>88672.60000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>272</v>
+      </c>
+      <c r="B13" t="n">
+        <v>83054.10000000001</v>
+      </c>
+      <c r="C13" t="n">
+        <v>76711.39999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>89174.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>273</v>
+      </c>
+      <c r="B14" t="n">
+        <v>83256.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>76898.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>89392.10000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>274</v>
+      </c>
+      <c r="B15" t="n">
+        <v>83184.8</v>
+      </c>
+      <c r="C15" t="n">
+        <v>76784.89999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>89229.10000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>275</v>
+      </c>
+      <c r="B16" t="n">
+        <v>82837.60000000001</v>
+      </c>
+      <c r="C16" t="n">
+        <v>76464.39999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>88856.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>276</v>
+      </c>
+      <c r="B17" t="n">
+        <v>82221.3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>75895.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>88195.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>277</v>
+      </c>
+      <c r="B18" t="n">
+        <v>81349.89999999999</v>
+      </c>
+      <c r="C18" t="n">
+        <v>75091.10000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>87260.8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>278</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80244.2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>74070.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>86074.8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>279</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78930.60000000001</v>
+      </c>
+      <c r="C20" t="n">
+        <v>72858</v>
+      </c>
+      <c r="D20" t="n">
+        <v>84665.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>280</v>
+      </c>
+      <c r="B21" t="n">
+        <v>77439</v>
+      </c>
+      <c r="C21" t="n">
+        <v>71481.10000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>83065.7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>281</v>
+      </c>
+      <c r="B22" t="n">
+        <v>75801</v>
+      </c>
+      <c r="C22" t="n">
+        <v>69969.10000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>81308.7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>282</v>
+      </c>
+      <c r="B23" t="n">
+        <v>74048.3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>68351.3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>79428.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>283</v>
+      </c>
+      <c r="B24" t="n">
+        <v>72211.5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>66655.8</v>
+      </c>
+      <c r="D24" t="n">
+        <v>77458.39999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>284</v>
+      </c>
+      <c r="B25" t="n">
+        <v>70319.10000000001</v>
+      </c>
+      <c r="C25" t="n">
+        <v>64909</v>
+      </c>
+      <c r="D25" t="n">
+        <v>75428.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>285</v>
+      </c>
+      <c r="B26" t="n">
+        <v>68396.89999999999</v>
+      </c>
+      <c r="C26" t="n">
+        <v>63134.7</v>
+      </c>
+      <c r="D26" t="n">
+        <v>73366.7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>286</v>
+      </c>
+      <c r="B27" t="n">
+        <v>66468.89999999999</v>
+      </c>
+      <c r="C27" t="n">
+        <v>61355</v>
+      </c>
+      <c r="D27" t="n">
+        <v>71298.60000000001</v>
       </c>
     </row>
   </sheetData>
@@ -55081,676 +55300,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>week_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>demand_forecast</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>demand_p10</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>demand_p90</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>261</v>
-      </c>
-      <c r="B2" t="n">
-        <v>67688.7</v>
-      </c>
-      <c r="C2" t="n">
-        <v>62317.2</v>
-      </c>
-      <c r="D2" t="n">
-        <v>73059.7</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>262</v>
-      </c>
-      <c r="B3" t="n">
-        <v>69682.89999999999</v>
-      </c>
-      <c r="C3" t="n">
-        <v>64153.1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>75212.10000000001</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>263</v>
-      </c>
-      <c r="B4" t="n">
-        <v>71623.60000000001</v>
-      </c>
-      <c r="C4" t="n">
-        <v>65939.8</v>
-      </c>
-      <c r="D4" t="n">
-        <v>77306.8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>264</v>
-      </c>
-      <c r="B5" t="n">
-        <v>73488.39999999999</v>
-      </c>
-      <c r="C5" t="n">
-        <v>67656.7</v>
-      </c>
-      <c r="D5" t="n">
-        <v>79319.60000000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>265</v>
-      </c>
-      <c r="B6" t="n">
-        <v>75256</v>
-      </c>
-      <c r="C6" t="n">
-        <v>69508.7</v>
-      </c>
-      <c r="D6" t="n">
-        <v>80801.89999999999</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>266</v>
-      </c>
-      <c r="B7" t="n">
-        <v>76904.89999999999</v>
-      </c>
-      <c r="C7" t="n">
-        <v>71031.7</v>
-      </c>
-      <c r="D7" t="n">
-        <v>82572.39999999999</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>267</v>
-      </c>
-      <c r="B8" t="n">
-        <v>78413.39999999999</v>
-      </c>
-      <c r="C8" t="n">
-        <v>72425</v>
-      </c>
-      <c r="D8" t="n">
-        <v>84192</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>268</v>
-      </c>
-      <c r="B9" t="n">
-        <v>79758.89999999999</v>
-      </c>
-      <c r="C9" t="n">
-        <v>73667.8</v>
-      </c>
-      <c r="D9" t="n">
-        <v>85636.7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>269</v>
-      </c>
-      <c r="B10" t="n">
-        <v>80918.2</v>
-      </c>
-      <c r="C10" t="n">
-        <v>74738.5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>86881.39999999999</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>270</v>
-      </c>
-      <c r="B11" t="n">
-        <v>81868</v>
-      </c>
-      <c r="C11" t="n">
-        <v>75615.8</v>
-      </c>
-      <c r="D11" t="n">
-        <v>87901.2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>271</v>
-      </c>
-      <c r="B12" t="n">
-        <v>82586.39999999999</v>
-      </c>
-      <c r="C12" t="n">
-        <v>76279.3</v>
-      </c>
-      <c r="D12" t="n">
-        <v>88672.60000000001</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>272</v>
-      </c>
-      <c r="B13" t="n">
-        <v>83054.10000000001</v>
-      </c>
-      <c r="C13" t="n">
-        <v>76711.39999999999</v>
-      </c>
-      <c r="D13" t="n">
-        <v>89174.8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>273</v>
-      </c>
-      <c r="B14" t="n">
-        <v>83256.5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>76898.3</v>
-      </c>
-      <c r="D14" t="n">
-        <v>89392.10000000001</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>274</v>
-      </c>
-      <c r="B15" t="n">
-        <v>83184.8</v>
-      </c>
-      <c r="C15" t="n">
-        <v>76784.89999999999</v>
-      </c>
-      <c r="D15" t="n">
-        <v>89229.10000000001</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>275</v>
-      </c>
-      <c r="B16" t="n">
-        <v>82837.60000000001</v>
-      </c>
-      <c r="C16" t="n">
-        <v>76464.39999999999</v>
-      </c>
-      <c r="D16" t="n">
-        <v>88856.7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>276</v>
-      </c>
-      <c r="B17" t="n">
-        <v>82221.3</v>
-      </c>
-      <c r="C17" t="n">
-        <v>75895.5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>88195.5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>277</v>
-      </c>
-      <c r="B18" t="n">
-        <v>81349.89999999999</v>
-      </c>
-      <c r="C18" t="n">
-        <v>75091.10000000001</v>
-      </c>
-      <c r="D18" t="n">
-        <v>87260.8</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>278</v>
-      </c>
-      <c r="B19" t="n">
-        <v>80244.2</v>
-      </c>
-      <c r="C19" t="n">
-        <v>74070.5</v>
-      </c>
-      <c r="D19" t="n">
-        <v>86074.8</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>279</v>
-      </c>
-      <c r="B20" t="n">
-        <v>78930.60000000001</v>
-      </c>
-      <c r="C20" t="n">
-        <v>72858</v>
-      </c>
-      <c r="D20" t="n">
-        <v>84665.8</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>280</v>
-      </c>
-      <c r="B21" t="n">
-        <v>77439</v>
-      </c>
-      <c r="C21" t="n">
-        <v>71481.10000000001</v>
-      </c>
-      <c r="D21" t="n">
-        <v>83065.7</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>281</v>
-      </c>
-      <c r="B22" t="n">
-        <v>75801</v>
-      </c>
-      <c r="C22" t="n">
-        <v>69969.10000000001</v>
-      </c>
-      <c r="D22" t="n">
-        <v>81308.7</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>282</v>
-      </c>
-      <c r="B23" t="n">
-        <v>74048.3</v>
-      </c>
-      <c r="C23" t="n">
-        <v>68351.3</v>
-      </c>
-      <c r="D23" t="n">
-        <v>79428.7</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>283</v>
-      </c>
-      <c r="B24" t="n">
-        <v>72211.5</v>
-      </c>
-      <c r="C24" t="n">
-        <v>66655.8</v>
-      </c>
-      <c r="D24" t="n">
-        <v>77458.39999999999</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>284</v>
-      </c>
-      <c r="B25" t="n">
-        <v>70319.10000000001</v>
-      </c>
-      <c r="C25" t="n">
-        <v>64909</v>
-      </c>
-      <c r="D25" t="n">
-        <v>75428.5</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>285</v>
-      </c>
-      <c r="B26" t="n">
-        <v>68396.89999999999</v>
-      </c>
-      <c r="C26" t="n">
-        <v>63134.7</v>
-      </c>
-      <c r="D26" t="n">
-        <v>73366.7</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>286</v>
-      </c>
-      <c r="B27" t="n">
-        <v>66468.89999999999</v>
-      </c>
-      <c r="C27" t="n">
-        <v>61355</v>
-      </c>
-      <c r="D27" t="n">
-        <v>71298.60000000001</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>segment</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>coverage (nominal 80%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>high_stock</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.7995</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.8014</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>all products</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.801</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="140" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Topic</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Assumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Reconstructed latent demand (demand_est) from the preprocessing notebook.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Horizon</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>26 weeks after week 260 on the synthetic calendar (week 1 = 2020-01-06).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>F3</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>No data leakage</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Each model and each tuning step only sees weeks up to the origin; legacy Demand_Forecast is not used as a model input (it does not exist for future weeks).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>F4</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Hyper-parameters</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Chosen on training data only: inner time-series CV (structural, Prophet), AICc (ETS, SARIMAX), trailing validation block with early stopping (LightGBM).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Metrics</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>WAPE is the primary metric (robust to small values); MAPE is reported as required; MASE scales by in-sample seasonal-naive error.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>F6</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Truth cells</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Weeks where stock never limited sales (unconstrained) have demand = observed sales; metrics on them do not depend on the reconstruction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>F7</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Ensembles</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>ens_mean uses 5 pre-declared members; ens_wf picks its top-3 only from earlier folds (walk-forward).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>F8</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Intervals</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Empirical quantiles of actual/forecast ratios from the selected model's backtests, by segment and horizon bucket.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>F9</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Stock scenario</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Future stock is unknown; expected sales are simulated with each product's own last-104-week stock-availability history.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>F10</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Prices</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Expected revenue uses the last-13-week mean price; no price changes assumed.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>